--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617446</v>
+        <v>122617929</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593050</v>
+        <v>593182</v>
       </c>
       <c r="R2" t="n">
-        <v>6375668</v>
+        <v>6375788</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617929</v>
+        <v>122617543</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,26 +829,17 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593182</v>
+        <v>593080</v>
       </c>
       <c r="R3" t="n">
-        <v>6375788</v>
+        <v>6375679</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617543</v>
+        <v>122617446</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>90853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593080</v>
+        <v>593050</v>
       </c>
       <c r="R4" t="n">
-        <v>6375679</v>
+        <v>6375668</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617929</v>
+        <v>122617543</v>
       </c>
       <c r="B2" t="n">
         <v>95011</v>
@@ -708,26 +708,17 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593182</v>
+        <v>593080</v>
       </c>
       <c r="R2" t="n">
-        <v>6375788</v>
+        <v>6375679</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617543</v>
+        <v>122617929</v>
       </c>
       <c r="B3" t="n">
         <v>95011</v>
@@ -829,17 +820,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593080</v>
+        <v>593182</v>
       </c>
       <c r="R3" t="n">
-        <v>6375679</v>
+        <v>6375788</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617543</v>
+        <v>122617929</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,17 +708,26 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593080</v>
+        <v>593182</v>
       </c>
       <c r="R2" t="n">
-        <v>6375679</v>
+        <v>6375788</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617929</v>
+        <v>122617446</v>
       </c>
       <c r="B3" t="n">
-        <v>95011</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +808,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593182</v>
+        <v>593050</v>
       </c>
       <c r="R3" t="n">
-        <v>6375788</v>
+        <v>6375668</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617446</v>
+        <v>122617543</v>
       </c>
       <c r="B4" t="n">
-        <v>90853</v>
+        <v>95012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593050</v>
+        <v>593080</v>
       </c>
       <c r="R4" t="n">
-        <v>6375668</v>
+        <v>6375679</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617929</v>
+        <v>122617914</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,16 +708,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617446</v>
+        <v>122617543</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>95126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593050</v>
+        <v>593080</v>
       </c>
       <c r="R3" t="n">
-        <v>6375668</v>
+        <v>6375679</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617543</v>
+        <v>122617446</v>
       </c>
       <c r="B4" t="n">
-        <v>95118</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593080</v>
+        <v>593050</v>
       </c>
       <c r="R4" t="n">
-        <v>6375679</v>
+        <v>6375668</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617914</v>
+        <v>122617929</v>
       </c>
       <c r="B2" t="n">
         <v>95126</v>
@@ -708,7 +708,16 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617929</v>
+        <v>122617543</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,26 +708,17 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593182</v>
+        <v>593080</v>
       </c>
       <c r="R2" t="n">
-        <v>6375788</v>
+        <v>6375679</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617543</v>
+        <v>122617914</v>
       </c>
       <c r="B3" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593080</v>
+        <v>593182</v>
       </c>
       <c r="R3" t="n">
-        <v>6375679</v>
+        <v>6375788</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617543</v>
+        <v>122617914</v>
       </c>
       <c r="B2" t="n">
         <v>95128</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593080</v>
+        <v>593182</v>
       </c>
       <c r="R2" t="n">
-        <v>6375679</v>
+        <v>6375788</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617914</v>
+        <v>122617446</v>
       </c>
       <c r="B3" t="n">
-        <v>95128</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593182</v>
+        <v>593050</v>
       </c>
       <c r="R3" t="n">
-        <v>6375788</v>
+        <v>6375668</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617446</v>
+        <v>122617543</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593050</v>
+        <v>593080</v>
       </c>
       <c r="R4" t="n">
-        <v>6375668</v>
+        <v>6375679</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122617914</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122617446</v>
+        <v>122617543</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593050</v>
+        <v>593080</v>
       </c>
       <c r="R3" t="n">
-        <v>6375668</v>
+        <v>6375679</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617543</v>
+        <v>122617446</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593080</v>
+        <v>593050</v>
       </c>
       <c r="R4" t="n">
-        <v>6375679</v>
+        <v>6375668</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617914</v>
+        <v>122617929</v>
       </c>
       <c r="B2" t="n">
         <v>95136</v>
@@ -708,7 +708,16 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ängkärret, Ängkärret, Sm</t>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,312 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123284883</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57657</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6375727</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123284624</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6375757</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123284370</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95136</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592989</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6375629</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284624</v>
+        <v>123284370</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593000</v>
+        <v>592989</v>
       </c>
       <c r="R6" t="n">
-        <v>6375757</v>
+        <v>6375629</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B7" t="n">
-        <v>95136</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R7" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284883</v>
+        <v>123284370</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>95139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102623</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593097</v>
+        <v>592989</v>
       </c>
       <c r="R5" t="n">
-        <v>6375727</v>
+        <v>6375629</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284370</v>
+        <v>123284883</v>
       </c>
       <c r="B6" t="n">
-        <v>95136</v>
+        <v>57660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592989</v>
+        <v>593097</v>
       </c>
       <c r="R6" t="n">
-        <v>6375629</v>
+        <v>6375727</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>123284624</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284370</v>
+        <v>123284883</v>
       </c>
       <c r="B5" t="n">
-        <v>95139</v>
+        <v>57660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592989</v>
+        <v>593097</v>
       </c>
       <c r="R5" t="n">
-        <v>6375629</v>
+        <v>6375727</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284883</v>
+        <v>123284624</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,20 +1134,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593097</v>
+        <v>593000</v>
       </c>
       <c r="R6" t="n">
-        <v>6375727</v>
+        <v>6375757</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284624</v>
+        <v>123284370</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>95141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593000</v>
+        <v>592989</v>
       </c>
       <c r="R7" t="n">
-        <v>6375757</v>
+        <v>6375629</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284624</v>
+        <v>123284370</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>95147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593000</v>
+        <v>592989</v>
       </c>
       <c r="R6" t="n">
-        <v>6375757</v>
+        <v>6375629</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B7" t="n">
-        <v>95141</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R7" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284624</v>
+        <v>123284370</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>95167</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593000</v>
+        <v>592989</v>
       </c>
       <c r="R5" t="n">
-        <v>6375757</v>
+        <v>6375629</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B6" t="n">
-        <v>95150</v>
+        <v>57503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R6" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>123284883</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>123284370</v>
       </c>
       <c r="B5" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284624</v>
+        <v>123284883</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>57669</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,20 +1134,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593000</v>
+        <v>593097</v>
       </c>
       <c r="R6" t="n">
-        <v>6375757</v>
+        <v>6375727</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284883</v>
+        <v>123284624</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,20 +1236,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593097</v>
+        <v>593000</v>
       </c>
       <c r="R7" t="n">
-        <v>6375727</v>
+        <v>6375757</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B5" t="n">
-        <v>95173</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R5" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284883</v>
+        <v>123284370</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593097</v>
+        <v>592989</v>
       </c>
       <c r="R6" t="n">
-        <v>6375727</v>
+        <v>6375629</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284624</v>
+        <v>123284883</v>
       </c>
       <c r="B7" t="n">
-        <v>57506</v>
+        <v>57670</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,20 +1236,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593000</v>
+        <v>593097</v>
       </c>
       <c r="R7" t="n">
-        <v>6375757</v>
+        <v>6375727</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284624</v>
+        <v>123284370</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593000</v>
+        <v>592989</v>
       </c>
       <c r="R5" t="n">
-        <v>6375757</v>
+        <v>6375629</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R6" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284624</v>
+        <v>123284883</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57670</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,20 +1134,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593000</v>
+        <v>593097</v>
       </c>
       <c r="R6" t="n">
-        <v>6375757</v>
+        <v>6375727</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284883</v>
+        <v>123284624</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,20 +1236,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593097</v>
+        <v>593000</v>
       </c>
       <c r="R7" t="n">
-        <v>6375727</v>
+        <v>6375757</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284370</v>
+        <v>123284624</v>
       </c>
       <c r="B5" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592989</v>
+        <v>593000</v>
       </c>
       <c r="R5" t="n">
-        <v>6375629</v>
+        <v>6375757</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284883</v>
+        <v>123284370</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593097</v>
+        <v>592989</v>
       </c>
       <c r="R6" t="n">
-        <v>6375727</v>
+        <v>6375629</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284624</v>
+        <v>123284883</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57670</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,20 +1236,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102623</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593000</v>
+        <v>593097</v>
       </c>
       <c r="R7" t="n">
-        <v>6375757</v>
+        <v>6375727</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122617929</v>
+        <v>122617388</v>
       </c>
       <c r="B2" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ängkärret, Ängkärret, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593182</v>
+        <v>593062</v>
       </c>
       <c r="R2" t="n">
-        <v>6375788</v>
+        <v>6375611</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +794,7 @@
         <v>122617543</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,37 +898,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122617446</v>
+        <v>122617914</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593050</v>
+        <v>593182</v>
       </c>
       <c r="R4" t="n">
-        <v>6375668</v>
+        <v>6375788</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,53 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123284624</v>
+        <v>123283959</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedgölen, Smedgölen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593000</v>
+        <v>593061</v>
       </c>
       <c r="R5" t="n">
-        <v>6375757</v>
+        <v>6375612</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284370</v>
+        <v>123284099</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,17 +1133,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedgölen, Smedgölen, Sm</t>
+          <t>Nymossen, Nymossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592989</v>
+        <v>593046</v>
       </c>
       <c r="R6" t="n">
-        <v>6375629</v>
+        <v>6375595</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,27 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284883</v>
+        <v>123284370</v>
       </c>
       <c r="B7" t="n">
-        <v>57670</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102623</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593097</v>
+        <v>592989</v>
       </c>
       <c r="R7" t="n">
-        <v>6375727</v>
+        <v>6375629</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,6 +1293,404 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122617446</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ängkärret, Ängkärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593050</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6375668</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123284245</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593019</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6375614</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123284624</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6375757</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123284883</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593097</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6375727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6993-2025 artfynd.xlsx
+++ b/artfynd/A 6993-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617388</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617914</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283959</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284099</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284370</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122617446</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284245</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284624</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,8 +1741,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>